--- a/data/examples/demo_data.xlsx
+++ b/data/examples/demo_data.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Employee Directory</t>
   </si>
@@ -26,10 +26,7 @@
     <t>Start Date</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>John Doe</t>
+    <t>Alice Smith</t>
   </si>
   <si>
     <t>Engineering</t>
@@ -41,112 +38,88 @@
     <t>2021-03-15</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>Jane Smith</t>
+    <t>Bob Johnson</t>
   </si>
   <si>
     <t>Marketing</t>
   </si>
   <si>
-    <t>Marketing Specialist</t>
+    <t>Marketing Manager</t>
+  </si>
+  <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
+    <t>Charlie Brown</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>HR Specialist</t>
   </si>
   <si>
     <t>2022-01-20</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>Peter Jones</t>
+    <t>Diana Prince</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Sales Manager</t>
+    <t>Sales Representative</t>
   </si>
   <si>
     <t>2020-07-01</t>
   </si>
   <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>Alice Brown</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>Operations Analyst</t>
-  </si>
-  <si>
-    <t>2023-05-10</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
-    <t>Robert Green</t>
+    <t>Ethan Hunt</t>
   </si>
   <si>
     <t>Engineering</t>
   </si>
   <si>
-    <t>Senior Developer</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>Maria Garcia</t>
+    <t>Lead Software Engineer</t>
+  </si>
+  <si>
+    <t>2018-05-10</t>
+  </si>
+  <si>
+    <t>Fiona Glenn</t>
   </si>
   <si>
     <t>Marketing</t>
   </si>
   <si>
-    <t>Content Creator</t>
-  </si>
-  <si>
-    <t>2022-09-01</t>
-  </si>
-  <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>David Lee</t>
+    <t>Content Strategist</t>
+  </si>
+  <si>
+    <t>2023-02-01</t>
+  </si>
+  <si>
+    <t>George Costanza</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Recruitment Coordinator</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>Hannah Abbott</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Account Executive</t>
-  </si>
-  <si>
-    <t>2023-02-15</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>Susan White</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>Logistics Coordinator</t>
-  </si>
-  <si>
-    <t>2021-06-01</t>
-  </si>
-  <si>
-    <t>Berlin</t>
+    <t>Sales Director</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
   </si>
   <si>
     <t>Department Overview</t>
@@ -161,19 +134,13 @@
     <t>Budget</t>
   </si>
   <si>
-    <t>Office Location</t>
-  </si>
-  <si>
     <t>Engineering</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>$5,200,000</t>
-  </si>
-  <si>
-    <t>New York HQ</t>
+    <t>35</t>
+  </si>
+  <si>
+    <t>$5,000,000</t>
   </si>
   <si>
     <t>Marketing</t>
@@ -182,34 +149,25 @@
     <t>20</t>
   </si>
   <si>
-    <t>$2,800,000</t>
-  </si>
-  <si>
-    <t>London Office</t>
+    <t>$3,000,000</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>$1,500,000</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>$3,500,000</t>
-  </si>
-  <si>
-    <t>Paris Tower</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>$1,800,000</t>
-  </si>
-  <si>
-    <t>Berlin Logistics Center</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>$4,500,000</t>
   </si>
 </sst>
 </file>
@@ -245,6 +203,9 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
@@ -269,144 +230,117 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -418,7 +352,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -426,69 +360,54 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/examples/demo_data.xlsx
+++ b/data/examples/demo_data.xlsx
@@ -9,9 +9,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
-  <si>
-    <t>Employee Directory</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+  <si>
+    <t>Employee Directory - Sheet 1</t>
   </si>
   <si>
     <t>Name</t>
@@ -26,7 +26,7 @@
     <t>Start Date</t>
   </si>
   <si>
-    <t>Alice Smith</t>
+    <t>Alice Johnson</t>
   </si>
   <si>
     <t>Engineering</t>
@@ -35,10 +35,10 @@
     <t>Software Engineer</t>
   </si>
   <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>Bob Johnson</t>
+    <t>2022-01-15</t>
+  </si>
+  <si>
+    <t>Bob Williams</t>
   </si>
   <si>
     <t>Marketing</t>
@@ -47,10 +47,22 @@
     <t>Marketing Manager</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>Charlie Brown</t>
+    <t>2021-06-01</t>
+  </si>
+  <si>
+    <t>Carol Davis</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Account Executive</t>
+  </si>
+  <si>
+    <t>2023-03-10</t>
+  </si>
+  <si>
+    <t>David Brown</t>
   </si>
   <si>
     <t>Human Resources</t>
@@ -59,115 +71,70 @@
     <t>HR Specialist</t>
   </si>
   <si>
-    <t>2022-01-20</t>
-  </si>
-  <si>
-    <t>Diana Prince</t>
+    <t>2022-11-01</t>
+  </si>
+  <si>
+    <t>Employee Directory - Sheet 2</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Eve Miller</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>QA Tester</t>
+  </si>
+  <si>
+    <t>2023-01-20</t>
+  </si>
+  <si>
+    <t>Frank White</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>Grace Lee</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Social Media Coordinator</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>Henry Green</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Sales Representative</t>
+    <t>Sales Director</t>
   </si>
   <si>
     <t>2020-07-01</t>
-  </si>
-  <si>
-    <t>Ethan Hunt</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Lead Software Engineer</t>
-  </si>
-  <si>
-    <t>2018-05-10</t>
-  </si>
-  <si>
-    <t>Fiona Glenn</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Content Strategist</t>
-  </si>
-  <si>
-    <t>2023-02-01</t>
-  </si>
-  <si>
-    <t>George Costanza</t>
-  </si>
-  <si>
-    <t>Human Resources</t>
-  </si>
-  <si>
-    <t>Recruitment Coordinator</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>Hannah Abbott</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>Sales Director</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>Department Overview</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Head Count</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>$5,000,000</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>$3,000,000</t>
-  </si>
-  <si>
-    <t>Human Resources</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>$1,500,000</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>$4,500,000</t>
   </si>
 </sst>
 </file>
@@ -287,62 +254,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -352,62 +263,77 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>42</v>
-      </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
